--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD5B339-30A1-4C71-A9BC-E8C90D6B7BBD}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9529038F-41B4-4019-AB99-80265D3DA234}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,21 @@
   </si>
   <si>
     <t>Felling very tired.</t>
+  </si>
+  <si>
+    <t>CA: English and DBMS</t>
+  </si>
+  <si>
+    <t>Python CA 15MCQ  2Coding Ques</t>
+  </si>
+  <si>
+    <t>Python CA</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Practice makes a man perfect.</t>
   </si>
 </sst>
 </file>
@@ -1832,136 +1847,280 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46090</v>
+      </c>
+      <c r="B22" s="14">
+        <v>310</v>
+      </c>
+      <c r="C22" s="14">
+        <v>34</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>65</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>30</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>759</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>681</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46121</v>
+      </c>
+      <c r="B23" s="14">
+        <v>326</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>55</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>90</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>871</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>569</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46151</v>
+      </c>
+      <c r="B24" s="14">
+        <v>319.142857142857</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>130</v>
+      </c>
+      <c r="E24" s="14">
+        <v>45</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>754.142857142857</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>685.857142857143</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46182</v>
+      </c>
+      <c r="B25" s="14">
+        <v>412</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>90</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>592</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>848</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46212</v>
+      </c>
+      <c r="B26" s="14">
+        <v>305.42857142857099</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>69</v>
+      </c>
+      <c r="E26" s="14">
+        <v>45</v>
+      </c>
+      <c r="F26" s="14">
+        <v>200</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>55</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>734.42857142857099</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>705.57142857142901</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B27" s="14">
+        <v>456</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>50</v>
+      </c>
+      <c r="E27" s="14">
+        <v>45</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>44</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>495</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9529038F-41B4-4019-AB99-80265D3DA234}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B88988C0-0113-4B85-B85C-C0061E961BEE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,33 @@
   </si>
   <si>
     <t>Practice makes a man perfect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time management </t>
+  </si>
+  <si>
+    <t>Wake up early</t>
+  </si>
+  <si>
+    <t>2026-13-09</t>
+  </si>
+  <si>
+    <t>Time never for stops anyone.</t>
+  </si>
+  <si>
+    <t>2026-14-09</t>
+  </si>
+  <si>
+    <t>2026-15-09</t>
+  </si>
+  <si>
+    <t>Mid term 3 oct</t>
+  </si>
+  <si>
+    <t>2026-16-09</t>
+  </si>
+  <si>
+    <t>Don't waste time</t>
   </si>
 </sst>
 </file>
@@ -2123,180 +2150,372 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>30</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>180</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B29" s="14">
+        <v>480</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
+        <v>49</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>240</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>969</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>471</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46335</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>40</v>
+      </c>
+      <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
+        <v>45</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46365</v>
+      </c>
+      <c r="B31" s="14">
+        <v>350</v>
+      </c>
+      <c r="C31" s="14">
+        <v>123</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>743</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>697</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="14">
+        <v>500</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>290</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="14">
+        <v>360</v>
+      </c>
+      <c r="C33" s="14">
+        <v>47</v>
+      </c>
+      <c r="D33" s="14">
+        <v>125</v>
+      </c>
+      <c r="E33" s="14">
+        <v>35</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>69</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>836</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>604</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="14">
+        <v>330</v>
+      </c>
+      <c r="C34" s="14">
+        <v>50</v>
+      </c>
+      <c r="D34" s="14">
+        <v>230</v>
+      </c>
+      <c r="E34" s="14">
+        <v>25</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>30</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="14">
+        <v>335</v>
+      </c>
+      <c r="C35" s="14">
+        <v>51</v>
+      </c>
+      <c r="D35" s="14">
+        <v>210</v>
+      </c>
+      <c r="E35" s="14">
+        <v>35</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1101</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>339</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12603513.xlsx
+++ b/12603513.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/830e508683434252/Desktop/CAP776 PYTHON MDMC/CAP776-PYTHON-MDMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B88988C0-0113-4B85-B85C-C0061E961BEE}"/>
+  <xr:revisionPtr revIDLastSave="458" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1C79AEA-F15B-4E2C-A964-FE887322B0A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,33 @@
   </si>
   <si>
     <t>Don't waste time</t>
+  </si>
+  <si>
+    <t>2026-17-09</t>
+  </si>
+  <si>
+    <t>Wake up early ershad</t>
+  </si>
+  <si>
+    <t>2026-18-09</t>
+  </si>
+  <si>
+    <t>2026-19-09</t>
+  </si>
+  <si>
+    <t>C++ CA</t>
+  </si>
+  <si>
+    <t>2026-20-09</t>
+  </si>
+  <si>
+    <t>Mid term coming</t>
+  </si>
+  <si>
+    <t>2026-21-09</t>
+  </si>
+  <si>
+    <t>Focus on your goal ershad</t>
   </si>
 </sst>
 </file>
@@ -2518,114 +2545,234 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>35</v>
+      </c>
+      <c r="D36" s="14">
+        <v>110</v>
+      </c>
+      <c r="E36" s="14">
+        <v>34</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>125</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>924</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>516</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="14">
+        <v>300</v>
+      </c>
+      <c r="C37" s="14">
+        <v>25</v>
+      </c>
+      <c r="D37" s="14">
+        <v>90</v>
+      </c>
+      <c r="E37" s="14">
+        <v>55</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>200</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>520</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="14">
+        <v>310</v>
+      </c>
+      <c r="C38" s="14">
+        <v>52</v>
+      </c>
+      <c r="D38" s="14">
+        <v>100</v>
+      </c>
+      <c r="E38" s="14">
+        <v>22</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>140</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>624</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>816</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="14">
+        <v>360</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>50</v>
+      </c>
+      <c r="E39" s="14">
+        <v>65</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>200</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+        <v>705</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="14">
+        <v>320</v>
+      </c>
+      <c r="C40" s="14">
+        <v>42</v>
+      </c>
+      <c r="D40" s="14">
+        <v>125</v>
+      </c>
+      <c r="E40" s="14">
+        <v>52</v>
+      </c>
+      <c r="F40" s="14">
+        <v>4</v>
+      </c>
+      <c r="G40" s="14">
+        <v>200</v>
+      </c>
+      <c r="H40" s="14">
+        <v>90</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>633</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>807</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
